--- a/data/ytd-budget.xlsx
+++ b/data/ytd-budget.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="189">
   <si>
     <t xml:space="preserve">FUND                          </t>
   </si>
@@ -351,15 +351,6 @@
   </si>
   <si>
     <t>Maint-IT Contracted Services</t>
-  </si>
-  <si>
-    <t>5222</t>
-  </si>
-  <si>
-    <t>100-30-340-5222-</t>
-  </si>
-  <si>
-    <t>Maint - Other Contractual Serv</t>
   </si>
   <si>
     <t>5311</t>
@@ -1070,8 +1061,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{551fcbe8-967d-4a12-b3db-590f41ef8508}">
-  <dimension ref="A1:Q60"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2f1f0111-3f0a-4b40-9d29-dd498c81d331}">
+  <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="16.8571428571429" style="3" customWidth="1"/>
@@ -1184,16 +1175,16 @@
         <v>8292176</v>
       </c>
       <c r="M2" s="7">
-        <v>6602660.7199999997</v>
+        <v>7213971.8300000001</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>1689515.28</v>
+        <v>1078204.17</v>
       </c>
       <c r="P2" s="7">
-        <v>79.60</v>
+        <v>87</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>20</v>
@@ -1237,16 +1228,16 @@
         <v>839233</v>
       </c>
       <c r="M3" s="7">
-        <v>897778.16</v>
+        <v>980162.33</v>
       </c>
       <c r="N3" s="7">
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <v>-58545.16</v>
+        <v>-140929.33</v>
       </c>
       <c r="P3" s="7">
-        <v>107</v>
+        <v>116.80</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>27</v>
@@ -1343,16 +1334,16 @@
         <v>7520</v>
       </c>
       <c r="M5" s="7">
-        <v>339.52</v>
+        <v>509.28</v>
       </c>
       <c r="N5" s="7">
         <v>0</v>
       </c>
       <c r="O5" s="5">
-        <v>7180.48</v>
+        <v>7010.72</v>
       </c>
       <c r="P5" s="7">
-        <v>4.50</v>
+        <v>6.80</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>20</v>
@@ -1449,16 +1440,16 @@
         <v>5304</v>
       </c>
       <c r="M7" s="7">
-        <v>4862</v>
+        <v>5304</v>
       </c>
       <c r="N7" s="7">
         <v>0</v>
       </c>
       <c r="O7" s="5">
-        <v>442</v>
+        <v>0</v>
       </c>
       <c r="P7" s="7">
-        <v>91.70</v>
+        <v>100</v>
       </c>
       <c r="Q7" s="3" t="s">
         <v>20</v>
@@ -1555,19 +1546,19 @@
         <v>16200</v>
       </c>
       <c r="M9" s="7">
-        <v>15900</v>
+        <v>16575</v>
       </c>
       <c r="N9" s="7">
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <v>300</v>
+        <v>-375</v>
       </c>
       <c r="P9" s="7">
-        <v>98.10</v>
+        <v>102.30</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="12.75">
@@ -1608,16 +1599,16 @@
         <v>1461990</v>
       </c>
       <c r="M10" s="7">
-        <v>1199430.80</v>
+        <v>1308585.83</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
       </c>
       <c r="O10" s="5">
-        <v>262559.20</v>
+        <v>153404.17</v>
       </c>
       <c r="P10" s="7">
-        <v>82</v>
+        <v>89.50</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>20</v>
@@ -1661,16 +1652,16 @@
         <v>652766</v>
       </c>
       <c r="M11" s="7">
-        <v>556814.71</v>
+        <v>608767.86</v>
       </c>
       <c r="N11" s="7">
         <v>0</v>
       </c>
       <c r="O11" s="5">
-        <v>95951.29</v>
+        <v>43998.14</v>
       </c>
       <c r="P11" s="7">
-        <v>85.30</v>
+        <v>93.30</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>20</v>
@@ -1714,16 +1705,16 @@
         <v>6178</v>
       </c>
       <c r="M12" s="7">
-        <v>13265.19</v>
+        <v>13268.42</v>
       </c>
       <c r="N12" s="7">
         <v>0</v>
       </c>
       <c r="O12" s="5">
-        <v>-7087.19</v>
+        <v>-7090.42</v>
       </c>
       <c r="P12" s="7">
-        <v>214.70</v>
+        <v>214.80</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>27</v>
@@ -1767,16 +1758,16 @@
         <v>1169536</v>
       </c>
       <c r="M13" s="7">
-        <v>877592.34</v>
+        <v>922154.42</v>
       </c>
       <c r="N13" s="7">
         <v>0</v>
       </c>
       <c r="O13" s="5">
-        <v>291943.66</v>
+        <v>247381.58</v>
       </c>
       <c r="P13" s="7">
-        <v>75</v>
+        <v>78.80</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>20</v>
@@ -1820,16 +1811,16 @@
         <v>68758</v>
       </c>
       <c r="M14" s="7">
-        <v>51752.69</v>
+        <v>54278.65</v>
       </c>
       <c r="N14" s="7">
         <v>0</v>
       </c>
       <c r="O14" s="5">
-        <v>17005.31</v>
+        <v>14479.35</v>
       </c>
       <c r="P14" s="7">
-        <v>75.30</v>
+        <v>78.90</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>20</v>
@@ -1873,16 +1864,16 @@
         <v>157601</v>
       </c>
       <c r="M15" s="7">
-        <v>136680.55</v>
+        <v>148525.54</v>
       </c>
       <c r="N15" s="7">
         <v>0</v>
       </c>
       <c r="O15" s="5">
-        <v>20920.45</v>
+        <v>9075.46</v>
       </c>
       <c r="P15" s="7">
-        <v>86.70</v>
+        <v>94.20</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>20</v>
@@ -1926,16 +1917,16 @@
         <v>42756</v>
       </c>
       <c r="M16" s="7">
-        <v>65479.12</v>
+        <v>65812.49</v>
       </c>
       <c r="N16" s="7">
         <v>0</v>
       </c>
       <c r="O16" s="5">
-        <v>-22723.12</v>
+        <v>-23056.49</v>
       </c>
       <c r="P16" s="7">
-        <v>153.10</v>
+        <v>153.90</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>27</v>
@@ -2244,16 +2235,16 @@
         <v>11560</v>
       </c>
       <c r="M22" s="7">
-        <v>7166.41</v>
+        <v>7393</v>
       </c>
       <c r="N22" s="7">
         <v>0</v>
       </c>
       <c r="O22" s="5">
-        <v>4393.59</v>
+        <v>4167</v>
       </c>
       <c r="P22" s="7">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>20</v>
@@ -2297,16 +2288,16 @@
         <v>186358</v>
       </c>
       <c r="M23" s="7">
-        <v>117684.65</v>
+        <v>126158.85</v>
       </c>
       <c r="N23" s="7">
-        <v>48902.14</v>
+        <v>41179.45</v>
       </c>
       <c r="O23" s="5">
-        <v>19771.21</v>
+        <v>19019.70</v>
       </c>
       <c r="P23" s="7">
-        <v>89.40</v>
+        <v>89.80</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>20</v>
@@ -2403,16 +2394,16 @@
         <v>100606</v>
       </c>
       <c r="M25" s="7">
-        <v>56123.37</v>
+        <v>57611.38</v>
       </c>
       <c r="N25" s="7">
-        <v>10341</v>
+        <v>16953.52</v>
       </c>
       <c r="O25" s="5">
-        <v>34141.63</v>
+        <v>26041.10</v>
       </c>
       <c r="P25" s="7">
-        <v>66.10</v>
+        <v>74.10</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>20</v>
@@ -2456,16 +2447,16 @@
         <v>146300</v>
       </c>
       <c r="M26" s="7">
-        <v>84985.76</v>
+        <v>91704.95</v>
       </c>
       <c r="N26" s="7">
-        <v>22096.64</v>
+        <v>19468.33</v>
       </c>
       <c r="O26" s="5">
-        <v>39217.60</v>
+        <v>35126.72</v>
       </c>
       <c r="P26" s="7">
-        <v>73.20</v>
+        <v>76</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>20</v>
@@ -2503,22 +2494,22 @@
         <v>92266</v>
       </c>
       <c r="K27" s="5">
-        <v>35000</v>
+        <v>115000</v>
       </c>
       <c r="L27" s="5">
-        <v>127266</v>
+        <v>207266</v>
       </c>
       <c r="M27" s="7">
-        <v>60592.61</v>
+        <v>61799.15</v>
       </c>
       <c r="N27" s="7">
-        <v>4373.50</v>
+        <v>71753.50</v>
       </c>
       <c r="O27" s="5">
-        <v>62299.89</v>
+        <v>73713.35</v>
       </c>
       <c r="P27" s="7">
-        <v>51</v>
+        <v>64.40</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>20</v>
@@ -2562,16 +2553,16 @@
         <v>235220</v>
       </c>
       <c r="M28" s="7">
-        <v>148506.33</v>
+        <v>158850.82</v>
       </c>
       <c r="N28" s="7">
-        <v>127566.48</v>
+        <v>121653.02</v>
       </c>
       <c r="O28" s="5">
-        <v>-40852.81</v>
+        <v>-45283.84</v>
       </c>
       <c r="P28" s="7">
-        <v>117.40</v>
+        <v>119.30</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>27</v>
@@ -2615,16 +2606,16 @@
         <v>79716</v>
       </c>
       <c r="M29" s="7">
-        <v>69674</v>
+        <v>69840.30</v>
       </c>
       <c r="N29" s="7">
         <v>0</v>
       </c>
       <c r="O29" s="5">
-        <v>10042</v>
+        <v>9875.70</v>
       </c>
       <c r="P29" s="7">
-        <v>87.40</v>
+        <v>87.60</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>20</v>
@@ -2759,34 +2750,34 @@
         <v>23</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="I32" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J32" s="5">
-        <v>0</v>
+        <v>514712</v>
       </c>
       <c r="K32" s="5">
         <v>0</v>
       </c>
       <c r="L32" s="5">
-        <v>0</v>
+        <v>514712</v>
       </c>
       <c r="M32" s="7">
-        <v>0</v>
+        <v>490748.50</v>
       </c>
       <c r="N32" s="7">
-        <v>0</v>
+        <v>77140</v>
       </c>
       <c r="O32" s="5">
-        <v>0</v>
+        <v>-53176.50</v>
       </c>
       <c r="P32" s="7">
-        <v>0</v>
+        <v>110.30</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="12.75">
@@ -2797,49 +2788,49 @@
         <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E33" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>118</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J33" s="5">
-        <v>514712</v>
+        <v>37082</v>
       </c>
       <c r="K33" s="5">
         <v>0</v>
       </c>
       <c r="L33" s="5">
-        <v>514712</v>
+        <v>37082</v>
       </c>
       <c r="M33" s="7">
-        <v>385700</v>
+        <v>39330.45</v>
       </c>
       <c r="N33" s="7">
-        <v>115710</v>
+        <v>0</v>
       </c>
       <c r="O33" s="5">
-        <v>13302</v>
+        <v>-2248.45</v>
       </c>
       <c r="P33" s="7">
-        <v>97.40</v>
+        <v>106.10</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:17" ht="12.75">
@@ -2865,34 +2856,34 @@
         <v>23</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I34" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J34" s="5">
-        <v>37082</v>
+        <v>22511</v>
       </c>
       <c r="K34" s="5">
         <v>0</v>
       </c>
       <c r="L34" s="5">
-        <v>37082</v>
+        <v>22511</v>
       </c>
       <c r="M34" s="7">
-        <v>39330.45</v>
+        <v>21461.50</v>
       </c>
       <c r="N34" s="7">
         <v>0</v>
       </c>
       <c r="O34" s="5">
-        <v>-2248.45</v>
+        <v>1049.50</v>
       </c>
       <c r="P34" s="7">
-        <v>106.10</v>
+        <v>95.30</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:17" ht="12.75">
@@ -2918,34 +2909,34 @@
         <v>23</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J35" s="5">
-        <v>22511</v>
+        <v>34076</v>
       </c>
       <c r="K35" s="5">
         <v>0</v>
       </c>
       <c r="L35" s="5">
-        <v>22511</v>
+        <v>34076</v>
       </c>
       <c r="M35" s="7">
-        <v>21461.50</v>
+        <v>35027</v>
       </c>
       <c r="N35" s="7">
         <v>0</v>
       </c>
       <c r="O35" s="5">
-        <v>1049.50</v>
+        <v>-951</v>
       </c>
       <c r="P35" s="7">
-        <v>95.30</v>
+        <v>102.80</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:17" ht="12.75">
@@ -2971,34 +2962,34 @@
         <v>23</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J36" s="5">
-        <v>34076</v>
+        <v>3650</v>
       </c>
       <c r="K36" s="5">
         <v>0</v>
       </c>
       <c r="L36" s="5">
-        <v>34076</v>
+        <v>3650</v>
       </c>
       <c r="M36" s="7">
-        <v>35027</v>
+        <v>3210.58</v>
       </c>
       <c r="N36" s="7">
         <v>0</v>
       </c>
       <c r="O36" s="5">
-        <v>-951</v>
+        <v>439.42</v>
       </c>
       <c r="P36" s="7">
-        <v>102.80</v>
+        <v>88</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:17" ht="12.75">
@@ -3024,34 +3015,34 @@
         <v>23</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J37" s="5">
-        <v>3650</v>
+        <v>53546</v>
       </c>
       <c r="K37" s="5">
         <v>0</v>
       </c>
       <c r="L37" s="5">
-        <v>3650</v>
+        <v>53546</v>
       </c>
       <c r="M37" s="7">
-        <v>224.31</v>
+        <v>53637.35</v>
       </c>
       <c r="N37" s="7">
-        <v>2883.25</v>
+        <v>0</v>
       </c>
       <c r="O37" s="5">
-        <v>542.44</v>
+        <v>-91.35</v>
       </c>
       <c r="P37" s="7">
-        <v>85.10</v>
+        <v>100.20</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="12.75">
@@ -3077,34 +3068,34 @@
         <v>23</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J38" s="5">
-        <v>53546</v>
+        <v>2550</v>
       </c>
       <c r="K38" s="5">
         <v>0</v>
       </c>
       <c r="L38" s="5">
-        <v>53546</v>
+        <v>2550</v>
       </c>
       <c r="M38" s="7">
-        <v>53637.35</v>
+        <v>1721.66</v>
       </c>
       <c r="N38" s="7">
         <v>0</v>
       </c>
       <c r="O38" s="5">
-        <v>-91.35</v>
+        <v>828.34</v>
       </c>
       <c r="P38" s="7">
-        <v>100.20</v>
+        <v>67.50</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="12.75">
@@ -3130,31 +3121,31 @@
         <v>23</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J39" s="5">
-        <v>2550</v>
+        <v>380967</v>
       </c>
       <c r="K39" s="5">
-        <v>0</v>
+        <v>-100000</v>
       </c>
       <c r="L39" s="5">
-        <v>2550</v>
+        <v>280967</v>
       </c>
       <c r="M39" s="7">
-        <v>1641.96</v>
+        <v>169648.98</v>
       </c>
       <c r="N39" s="7">
-        <v>0</v>
+        <v>16827.75</v>
       </c>
       <c r="O39" s="5">
-        <v>908.04</v>
+        <v>94490.27</v>
       </c>
       <c r="P39" s="7">
-        <v>64.40</v>
+        <v>66.40</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>20</v>
@@ -3183,34 +3174,34 @@
         <v>23</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J40" s="5">
-        <v>380967</v>
+        <v>45000</v>
       </c>
       <c r="K40" s="5">
-        <v>-20000</v>
+        <v>0</v>
       </c>
       <c r="L40" s="5">
-        <v>360967</v>
+        <v>45000</v>
       </c>
       <c r="M40" s="7">
-        <v>167148.98</v>
+        <v>33682.45</v>
       </c>
       <c r="N40" s="7">
-        <v>12027.75</v>
+        <v>18273.43</v>
       </c>
       <c r="O40" s="5">
-        <v>181790.27</v>
+        <v>-6955.88</v>
       </c>
       <c r="P40" s="7">
-        <v>49.60</v>
+        <v>115.50</v>
       </c>
       <c r="Q40" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:17" ht="12.75">
@@ -3236,31 +3227,31 @@
         <v>23</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J41" s="5">
-        <v>45000</v>
+        <v>21468</v>
       </c>
       <c r="K41" s="5">
         <v>0</v>
       </c>
       <c r="L41" s="5">
-        <v>45000</v>
+        <v>21468</v>
       </c>
       <c r="M41" s="7">
-        <v>33682.45</v>
+        <v>26164.67</v>
       </c>
       <c r="N41" s="7">
-        <v>18273.43</v>
+        <v>0</v>
       </c>
       <c r="O41" s="5">
-        <v>-6955.88</v>
+        <v>-4696.67</v>
       </c>
       <c r="P41" s="7">
-        <v>115.50</v>
+        <v>121.90</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>27</v>
@@ -3289,34 +3280,34 @@
         <v>23</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J42" s="5">
-        <v>21468</v>
+        <v>21300</v>
       </c>
       <c r="K42" s="5">
         <v>0</v>
       </c>
       <c r="L42" s="5">
-        <v>21468</v>
+        <v>21300</v>
       </c>
       <c r="M42" s="7">
-        <v>24170.01</v>
+        <v>14249.80</v>
       </c>
       <c r="N42" s="7">
-        <v>0</v>
+        <v>7050.20</v>
       </c>
       <c r="O42" s="5">
-        <v>-2702.01</v>
+        <v>0</v>
       </c>
       <c r="P42" s="7">
-        <v>112.60</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="3" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="12.75">
@@ -3342,31 +3333,31 @@
         <v>23</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J43" s="5">
-        <v>21300</v>
+        <v>14125</v>
       </c>
       <c r="K43" s="5">
         <v>0</v>
       </c>
       <c r="L43" s="5">
-        <v>21300</v>
+        <v>14125</v>
       </c>
       <c r="M43" s="7">
-        <v>13654.64</v>
+        <v>11857</v>
       </c>
       <c r="N43" s="7">
-        <v>7645.36</v>
+        <v>0</v>
       </c>
       <c r="O43" s="5">
-        <v>0</v>
+        <v>2268</v>
       </c>
       <c r="P43" s="7">
-        <v>100</v>
+        <v>83.90</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>20</v>
@@ -3395,31 +3386,31 @@
         <v>23</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J44" s="5">
-        <v>14125</v>
+        <v>28115</v>
       </c>
       <c r="K44" s="5">
         <v>0</v>
       </c>
       <c r="L44" s="5">
-        <v>14125</v>
+        <v>28115</v>
       </c>
       <c r="M44" s="7">
-        <v>10077.94</v>
+        <v>15778.01</v>
       </c>
       <c r="N44" s="7">
         <v>0</v>
       </c>
       <c r="O44" s="5">
-        <v>4047.06</v>
+        <v>12336.99</v>
       </c>
       <c r="P44" s="7">
-        <v>71.30</v>
+        <v>56.10</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>20</v>
@@ -3433,46 +3424,46 @@
         <v>18</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>155</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J45" s="5">
-        <v>28115</v>
+        <v>2550</v>
       </c>
       <c r="K45" s="5">
         <v>0</v>
       </c>
       <c r="L45" s="5">
-        <v>28115</v>
+        <v>2550</v>
       </c>
       <c r="M45" s="7">
-        <v>15178.01</v>
+        <v>11</v>
       </c>
       <c r="N45" s="7">
         <v>0</v>
       </c>
       <c r="O45" s="5">
-        <v>12936.99</v>
+        <v>2539</v>
       </c>
       <c r="P45" s="7">
-        <v>54</v>
+        <v>0.40</v>
       </c>
       <c r="Q45" s="3" t="s">
         <v>20</v>
@@ -3501,31 +3492,31 @@
         <v>23</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J46" s="5">
-        <v>2550</v>
+        <v>127285</v>
       </c>
       <c r="K46" s="5">
         <v>0</v>
       </c>
       <c r="L46" s="5">
-        <v>2550</v>
+        <v>127285</v>
       </c>
       <c r="M46" s="7">
-        <v>11</v>
+        <v>92153.01</v>
       </c>
       <c r="N46" s="7">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="O46" s="5">
-        <v>2539</v>
+        <v>32131.99</v>
       </c>
       <c r="P46" s="7">
-        <v>0.40</v>
+        <v>74.80</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>20</v>
@@ -3554,31 +3545,31 @@
         <v>23</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J47" s="5">
-        <v>127285</v>
+        <v>24890</v>
       </c>
       <c r="K47" s="5">
         <v>0</v>
       </c>
       <c r="L47" s="5">
-        <v>127285</v>
+        <v>24890</v>
       </c>
       <c r="M47" s="7">
-        <v>92153.01</v>
+        <v>24329.58</v>
       </c>
       <c r="N47" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="O47" s="5">
-        <v>32131.99</v>
+        <v>560.42</v>
       </c>
       <c r="P47" s="7">
-        <v>74.80</v>
+        <v>97.70</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>20</v>
@@ -3607,31 +3598,31 @@
         <v>23</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J48" s="5">
-        <v>24890</v>
+        <v>215021</v>
       </c>
       <c r="K48" s="5">
         <v>0</v>
       </c>
       <c r="L48" s="5">
-        <v>24890</v>
+        <v>215021</v>
       </c>
       <c r="M48" s="7">
-        <v>24329.58</v>
+        <v>131203.27</v>
       </c>
       <c r="N48" s="7">
-        <v>0</v>
+        <v>21072.83</v>
       </c>
       <c r="O48" s="5">
-        <v>560.42</v>
+        <v>62744.90</v>
       </c>
       <c r="P48" s="7">
-        <v>97.70</v>
+        <v>70.80</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>20</v>
@@ -3660,31 +3651,31 @@
         <v>23</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J49" s="5">
-        <v>215021</v>
+        <v>1650</v>
       </c>
       <c r="K49" s="5">
         <v>0</v>
       </c>
       <c r="L49" s="5">
-        <v>215021</v>
+        <v>1650</v>
       </c>
       <c r="M49" s="7">
-        <v>117357.73</v>
+        <v>298.89</v>
       </c>
       <c r="N49" s="7">
-        <v>27646.77</v>
+        <v>0</v>
       </c>
       <c r="O49" s="5">
-        <v>70016.50</v>
+        <v>1351.11</v>
       </c>
       <c r="P49" s="7">
-        <v>67.40</v>
+        <v>18.10</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>20</v>
@@ -3713,31 +3704,31 @@
         <v>23</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="I50" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J50" s="5">
-        <v>1650</v>
+        <v>197959</v>
       </c>
       <c r="K50" s="5">
         <v>0</v>
       </c>
       <c r="L50" s="5">
-        <v>1650</v>
+        <v>197959</v>
       </c>
       <c r="M50" s="7">
-        <v>298.89</v>
+        <v>148841.31</v>
       </c>
       <c r="N50" s="7">
         <v>0</v>
       </c>
       <c r="O50" s="5">
-        <v>1351.11</v>
+        <v>49117.69</v>
       </c>
       <c r="P50" s="7">
-        <v>18.10</v>
+        <v>75.20</v>
       </c>
       <c r="Q50" s="3" t="s">
         <v>20</v>
@@ -3751,46 +3742,46 @@
         <v>18</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G51" s="3" t="s">
         <v>23</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>174</v>
+        <v>20</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>20</v>
       </c>
       <c r="J51" s="5">
-        <v>197959</v>
+        <v>15000</v>
       </c>
       <c r="K51" s="5">
         <v>0</v>
       </c>
       <c r="L51" s="5">
-        <v>197959</v>
+        <v>15000</v>
       </c>
       <c r="M51" s="7">
-        <v>148841.31</v>
+        <v>0</v>
       </c>
       <c r="N51" s="7">
         <v>0</v>
       </c>
       <c r="O51" s="5">
-        <v>49117.69</v>
+        <v>15000</v>
       </c>
       <c r="P51" s="7">
-        <v>75.20</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="3" t="s">
         <v>20</v>
@@ -3825,25 +3816,25 @@
         <v>20</v>
       </c>
       <c r="J52" s="5">
-        <v>15000</v>
+        <v>63882</v>
       </c>
       <c r="K52" s="5">
         <v>0</v>
       </c>
       <c r="L52" s="5">
-        <v>15000</v>
+        <v>63882</v>
       </c>
       <c r="M52" s="7">
-        <v>0</v>
+        <v>63882</v>
       </c>
       <c r="N52" s="7">
         <v>0</v>
       </c>
       <c r="O52" s="5">
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="P52" s="7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>20</v>
@@ -3878,28 +3869,28 @@
         <v>20</v>
       </c>
       <c r="J53" s="5">
-        <v>63882</v>
+        <v>0</v>
       </c>
       <c r="K53" s="5">
         <v>0</v>
       </c>
       <c r="L53" s="5">
-        <v>63882</v>
+        <v>0</v>
       </c>
       <c r="M53" s="7">
-        <v>63882</v>
+        <v>9725</v>
       </c>
       <c r="N53" s="7">
         <v>0</v>
       </c>
       <c r="O53" s="5">
-        <v>0</v>
+        <v>-9725</v>
       </c>
       <c r="P53" s="7">
         <v>100</v>
       </c>
       <c r="Q53" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:17" ht="12.75">
@@ -3934,22 +3925,22 @@
         <v>0</v>
       </c>
       <c r="K54" s="5">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="L54" s="5">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="M54" s="7">
-        <v>9725</v>
+        <v>50231.96</v>
       </c>
       <c r="N54" s="7">
         <v>0</v>
       </c>
       <c r="O54" s="5">
-        <v>-9725</v>
+        <v>-10231.96</v>
       </c>
       <c r="P54" s="7">
-        <v>100</v>
+        <v>125.60</v>
       </c>
       <c r="Q54" s="3" t="s">
         <v>27</v>
@@ -3957,25 +3948,25 @@
     </row>
     <row r="55" spans="1:17" ht="12.75">
       <c r="A55" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>186</v>
-      </c>
       <c r="G55" s="3" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>20</v>
@@ -3984,25 +3975,25 @@
         <v>20</v>
       </c>
       <c r="J55" s="5">
-        <v>0</v>
+        <v>15662635</v>
       </c>
       <c r="K55" s="5">
-        <v>40000</v>
+        <v>10463.77</v>
       </c>
       <c r="L55" s="5">
-        <v>40000</v>
+        <v>15673098.77</v>
       </c>
       <c r="M55" s="7">
-        <v>50231.96</v>
+        <v>13511242.609999999</v>
       </c>
       <c r="N55" s="7">
-        <v>0</v>
+        <v>414372.03</v>
       </c>
       <c r="O55" s="5">
-        <v>-10231.96</v>
+        <v>1747484.13</v>
       </c>
       <c r="P55" s="7">
-        <v>125.60</v>
+        <v>88.90</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>27</v>
@@ -4010,10 +4001,10 @@
     </row>
     <row r="56" spans="1:17" ht="12.75">
       <c r="A56" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>20</v>
@@ -4025,7 +4016,7 @@
         <v>20</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G56" s="3" t="s">
         <v>20</v>
@@ -4046,16 +4037,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M56" s="7">
-        <v>12437828.550000001</v>
+        <v>13511242.609999999</v>
       </c>
       <c r="N56" s="7">
-        <v>400466.32</v>
+        <v>414372.03</v>
       </c>
       <c r="O56" s="5">
-        <v>2834803.90</v>
+        <v>1747484.13</v>
       </c>
       <c r="P56" s="7">
-        <v>81.90</v>
+        <v>88.90</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>27</v>
@@ -4063,7 +4054,7 @@
     </row>
     <row r="57" spans="1:17" ht="12.75">
       <c r="A57" s="3" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>20</v>
@@ -4078,7 +4069,7 @@
         <v>20</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="G57" s="3" t="s">
         <v>20</v>
@@ -4090,25 +4081,25 @@
         <v>20</v>
       </c>
       <c r="J57" s="5">
-        <v>15662635</v>
+        <v>0</v>
       </c>
       <c r="K57" s="5">
-        <v>10463.77</v>
+        <v>0</v>
       </c>
       <c r="L57" s="5">
-        <v>15673098.77</v>
+        <v>0</v>
       </c>
       <c r="M57" s="7">
-        <v>12437828.550000001</v>
+        <v>0</v>
       </c>
       <c r="N57" s="7">
-        <v>400466.32</v>
+        <v>0</v>
       </c>
       <c r="O57" s="5">
-        <v>2834803.90</v>
+        <v>0</v>
       </c>
       <c r="P57" s="7">
-        <v>81.90</v>
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>27</v>
@@ -4131,7 +4122,7 @@
         <v>20</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G58" s="3" t="s">
         <v>20</v>
@@ -4143,25 +4134,25 @@
         <v>20</v>
       </c>
       <c r="J58" s="5">
-        <v>0</v>
+        <v>15662635</v>
       </c>
       <c r="K58" s="5">
-        <v>0</v>
+        <v>10463.77</v>
       </c>
       <c r="L58" s="5">
-        <v>0</v>
+        <v>15673098.77</v>
       </c>
       <c r="M58" s="7">
-        <v>0</v>
+        <v>13511242.609999999</v>
       </c>
       <c r="N58" s="7">
-        <v>0</v>
+        <v>414372.03</v>
       </c>
       <c r="O58" s="5">
-        <v>0</v>
+        <v>1747484.13</v>
       </c>
       <c r="P58" s="7">
-        <v>0</v>
+        <v>88.90</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>27</v>
@@ -4184,7 +4175,7 @@
         <v>20</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G59" s="3" t="s">
         <v>20</v>
@@ -4205,71 +4196,18 @@
         <v>15673098.77</v>
       </c>
       <c r="M59" s="7">
-        <v>12437828.550000001</v>
+        <v>13511242.609999999</v>
       </c>
       <c r="N59" s="7">
-        <v>400466.32</v>
+        <v>414372.03</v>
       </c>
       <c r="O59" s="5">
-        <v>2834803.90</v>
+        <v>1747484.13</v>
       </c>
       <c r="P59" s="7">
-        <v>81.90</v>
+        <v>88.90</v>
       </c>
       <c r="Q59" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="12.75">
-      <c r="A60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J60" s="5">
-        <v>15662635</v>
-      </c>
-      <c r="K60" s="5">
-        <v>10463.77</v>
-      </c>
-      <c r="L60" s="5">
-        <v>15673098.77</v>
-      </c>
-      <c r="M60" s="7">
-        <v>12437828.550000001</v>
-      </c>
-      <c r="N60" s="7">
-        <v>400466.32</v>
-      </c>
-      <c r="O60" s="5">
-        <v>2834803.90</v>
-      </c>
-      <c r="P60" s="7">
-        <v>81.90</v>
-      </c>
-      <c r="Q60" s="3" t="s">
         <v>27</v>
       </c>
     </row>

--- a/data/ytd-budget.xlsx
+++ b/data/ytd-budget.xlsx
@@ -1061,7 +1061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2f1f0111-3f0a-4b40-9d29-dd498c81d331}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56107a29-9e84-47c9-938d-f3dcadf42edb}">
   <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -1175,16 +1175,16 @@
         <v>8292176</v>
       </c>
       <c r="M2" s="7">
-        <v>7213971.8300000001</v>
+        <v>7516766.8600000003</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>1078204.17</v>
+        <v>775409.14</v>
       </c>
       <c r="P2" s="7">
-        <v>87</v>
+        <v>90.60</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>20</v>
@@ -1228,16 +1228,16 @@
         <v>839233</v>
       </c>
       <c r="M3" s="7">
-        <v>980162.33</v>
+        <v>1026985</v>
       </c>
       <c r="N3" s="7">
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <v>-140929.33</v>
+        <v>-187752</v>
       </c>
       <c r="P3" s="7">
-        <v>116.80</v>
+        <v>122.40</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>27</v>
@@ -1546,16 +1546,16 @@
         <v>16200</v>
       </c>
       <c r="M9" s="7">
-        <v>16575</v>
+        <v>17250</v>
       </c>
       <c r="N9" s="7">
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <v>-375</v>
+        <v>-1050</v>
       </c>
       <c r="P9" s="7">
-        <v>102.30</v>
+        <v>106.50</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>27</v>
@@ -1599,16 +1599,16 @@
         <v>1461990</v>
       </c>
       <c r="M10" s="7">
-        <v>1308585.83</v>
+        <v>1363190.44</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
       </c>
       <c r="O10" s="5">
-        <v>153404.17</v>
+        <v>98799.56</v>
       </c>
       <c r="P10" s="7">
-        <v>89.50</v>
+        <v>93.20</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>20</v>
@@ -1652,16 +1652,16 @@
         <v>652766</v>
       </c>
       <c r="M11" s="7">
-        <v>608767.86</v>
+        <v>634182.67</v>
       </c>
       <c r="N11" s="7">
         <v>0</v>
       </c>
       <c r="O11" s="5">
-        <v>43998.14</v>
+        <v>18583.33</v>
       </c>
       <c r="P11" s="7">
-        <v>93.30</v>
+        <v>97.20</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>20</v>
@@ -1758,16 +1758,16 @@
         <v>1169536</v>
       </c>
       <c r="M13" s="7">
-        <v>922154.42</v>
+        <v>966140.27</v>
       </c>
       <c r="N13" s="7">
         <v>0</v>
       </c>
       <c r="O13" s="5">
-        <v>247381.58</v>
+        <v>203395.73</v>
       </c>
       <c r="P13" s="7">
-        <v>78.80</v>
+        <v>82.60</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>20</v>
@@ -1811,16 +1811,16 @@
         <v>68758</v>
       </c>
       <c r="M14" s="7">
-        <v>54278.65</v>
+        <v>39284.18</v>
       </c>
       <c r="N14" s="7">
         <v>0</v>
       </c>
       <c r="O14" s="5">
-        <v>14479.35</v>
+        <v>29473.82</v>
       </c>
       <c r="P14" s="7">
-        <v>78.90</v>
+        <v>57.10</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>20</v>
@@ -1864,16 +1864,16 @@
         <v>157601</v>
       </c>
       <c r="M15" s="7">
-        <v>148525.54</v>
+        <v>154500.79</v>
       </c>
       <c r="N15" s="7">
         <v>0</v>
       </c>
       <c r="O15" s="5">
-        <v>9075.46</v>
+        <v>3100.21</v>
       </c>
       <c r="P15" s="7">
-        <v>94.20</v>
+        <v>98</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>20</v>
@@ -1917,16 +1917,16 @@
         <v>42756</v>
       </c>
       <c r="M16" s="7">
-        <v>65812.49</v>
+        <v>66145.86</v>
       </c>
       <c r="N16" s="7">
         <v>0</v>
       </c>
       <c r="O16" s="5">
-        <v>-23056.49</v>
+        <v>-23389.86</v>
       </c>
       <c r="P16" s="7">
-        <v>153.90</v>
+        <v>154.70</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>27</v>
@@ -2129,16 +2129,16 @@
         <v>5000</v>
       </c>
       <c r="M20" s="7">
-        <v>2517.21</v>
+        <v>2725.29</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="5">
-        <v>2482.79</v>
+        <v>2274.71</v>
       </c>
       <c r="P20" s="7">
-        <v>50.30</v>
+        <v>54.50</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>20</v>
@@ -2182,16 +2182,16 @@
         <v>5023</v>
       </c>
       <c r="M21" s="7">
-        <v>3640.64</v>
+        <v>2226.25</v>
       </c>
       <c r="N21" s="7">
         <v>0</v>
       </c>
       <c r="O21" s="5">
-        <v>1382.36</v>
+        <v>2796.75</v>
       </c>
       <c r="P21" s="7">
-        <v>72.50</v>
+        <v>44.30</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>20</v>
@@ -2235,16 +2235,16 @@
         <v>11560</v>
       </c>
       <c r="M22" s="7">
-        <v>7393</v>
+        <v>8908.88</v>
       </c>
       <c r="N22" s="7">
         <v>0</v>
       </c>
       <c r="O22" s="5">
-        <v>4167</v>
+        <v>2651.12</v>
       </c>
       <c r="P22" s="7">
-        <v>64</v>
+        <v>77.10</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>20</v>
@@ -2288,16 +2288,16 @@
         <v>186358</v>
       </c>
       <c r="M23" s="7">
-        <v>126158.85</v>
+        <v>146689.26</v>
       </c>
       <c r="N23" s="7">
-        <v>41179.45</v>
+        <v>26519.68</v>
       </c>
       <c r="O23" s="5">
-        <v>19019.70</v>
+        <v>13149.06</v>
       </c>
       <c r="P23" s="7">
-        <v>89.80</v>
+        <v>92.90</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>20</v>
@@ -2341,19 +2341,19 @@
         <v>500</v>
       </c>
       <c r="M24" s="7">
-        <v>389.95</v>
+        <v>859.23</v>
       </c>
       <c r="N24" s="7">
         <v>0</v>
       </c>
       <c r="O24" s="5">
-        <v>110.05</v>
+        <v>-359.23</v>
       </c>
       <c r="P24" s="7">
-        <v>78</v>
+        <v>171.80</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="12.75">
@@ -2394,16 +2394,16 @@
         <v>100606</v>
       </c>
       <c r="M25" s="7">
-        <v>57611.38</v>
+        <v>64304.68</v>
       </c>
       <c r="N25" s="7">
-        <v>16953.52</v>
+        <v>11789.19</v>
       </c>
       <c r="O25" s="5">
-        <v>26041.10</v>
+        <v>24512.13</v>
       </c>
       <c r="P25" s="7">
-        <v>74.10</v>
+        <v>75.60</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>20</v>
@@ -2447,16 +2447,16 @@
         <v>146300</v>
       </c>
       <c r="M26" s="7">
-        <v>91704.95</v>
+        <v>101187.97</v>
       </c>
       <c r="N26" s="7">
-        <v>19468.33</v>
+        <v>13344.46</v>
       </c>
       <c r="O26" s="5">
-        <v>35126.72</v>
+        <v>31767.57</v>
       </c>
       <c r="P26" s="7">
-        <v>76</v>
+        <v>78.30</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>20</v>
@@ -2494,22 +2494,22 @@
         <v>92266</v>
       </c>
       <c r="K27" s="5">
-        <v>115000</v>
+        <v>89200</v>
       </c>
       <c r="L27" s="5">
-        <v>207266</v>
+        <v>181466</v>
       </c>
       <c r="M27" s="7">
-        <v>61799.15</v>
+        <v>66880.95</v>
       </c>
       <c r="N27" s="7">
         <v>71753.50</v>
       </c>
       <c r="O27" s="5">
-        <v>73713.35</v>
+        <v>42831.55</v>
       </c>
       <c r="P27" s="7">
-        <v>64.40</v>
+        <v>76.40</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>20</v>
@@ -2553,16 +2553,16 @@
         <v>235220</v>
       </c>
       <c r="M28" s="7">
-        <v>158850.82</v>
+        <v>163614.79</v>
       </c>
       <c r="N28" s="7">
-        <v>121653.02</v>
+        <v>123987.33</v>
       </c>
       <c r="O28" s="5">
-        <v>-45283.84</v>
+        <v>-52382.12</v>
       </c>
       <c r="P28" s="7">
-        <v>119.30</v>
+        <v>122.30</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>27</v>
@@ -2606,16 +2606,16 @@
         <v>79716</v>
       </c>
       <c r="M29" s="7">
-        <v>69840.30</v>
+        <v>71048.08</v>
       </c>
       <c r="N29" s="7">
         <v>0</v>
       </c>
       <c r="O29" s="5">
-        <v>9875.70</v>
+        <v>8667.92</v>
       </c>
       <c r="P29" s="7">
-        <v>87.60</v>
+        <v>89.10</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>20</v>
@@ -2765,10 +2765,10 @@
         <v>514712</v>
       </c>
       <c r="M32" s="7">
-        <v>490748.50</v>
+        <v>529318.50</v>
       </c>
       <c r="N32" s="7">
-        <v>77140</v>
+        <v>38570</v>
       </c>
       <c r="O32" s="5">
         <v>-53176.50</v>
@@ -3083,16 +3083,16 @@
         <v>2550</v>
       </c>
       <c r="M38" s="7">
-        <v>1721.66</v>
+        <v>1893.46</v>
       </c>
       <c r="N38" s="7">
         <v>0</v>
       </c>
       <c r="O38" s="5">
-        <v>828.34</v>
+        <v>656.54</v>
       </c>
       <c r="P38" s="7">
-        <v>67.50</v>
+        <v>74.30</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>20</v>
@@ -3136,16 +3136,16 @@
         <v>280967</v>
       </c>
       <c r="M39" s="7">
-        <v>169648.98</v>
+        <v>171749.98</v>
       </c>
       <c r="N39" s="7">
         <v>16827.75</v>
       </c>
       <c r="O39" s="5">
-        <v>94490.27</v>
+        <v>92389.27</v>
       </c>
       <c r="P39" s="7">
-        <v>66.40</v>
+        <v>67.10</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>20</v>
@@ -3189,16 +3189,16 @@
         <v>45000</v>
       </c>
       <c r="M40" s="7">
-        <v>33682.45</v>
+        <v>36280.34</v>
       </c>
       <c r="N40" s="7">
-        <v>18273.43</v>
+        <v>11794.89</v>
       </c>
       <c r="O40" s="5">
-        <v>-6955.88</v>
+        <v>-3075.23</v>
       </c>
       <c r="P40" s="7">
-        <v>115.50</v>
+        <v>106.80</v>
       </c>
       <c r="Q40" s="3" t="s">
         <v>27</v>
@@ -3242,16 +3242,16 @@
         <v>21468</v>
       </c>
       <c r="M41" s="7">
-        <v>26164.67</v>
+        <v>28615.60</v>
       </c>
       <c r="N41" s="7">
         <v>0</v>
       </c>
       <c r="O41" s="5">
-        <v>-4696.67</v>
+        <v>-7147.60</v>
       </c>
       <c r="P41" s="7">
-        <v>121.90</v>
+        <v>133.30</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>27</v>
@@ -3295,10 +3295,10 @@
         <v>21300</v>
       </c>
       <c r="M42" s="7">
-        <v>14249.80</v>
+        <v>14841.07</v>
       </c>
       <c r="N42" s="7">
-        <v>7050.20</v>
+        <v>6458.93</v>
       </c>
       <c r="O42" s="5">
         <v>0</v>
@@ -3348,16 +3348,16 @@
         <v>14125</v>
       </c>
       <c r="M43" s="7">
-        <v>11857</v>
+        <v>13003.26</v>
       </c>
       <c r="N43" s="7">
         <v>0</v>
       </c>
       <c r="O43" s="5">
-        <v>2268</v>
+        <v>1121.74</v>
       </c>
       <c r="P43" s="7">
-        <v>83.90</v>
+        <v>92.10</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>20</v>
@@ -3401,16 +3401,16 @@
         <v>28115</v>
       </c>
       <c r="M44" s="7">
-        <v>15778.01</v>
+        <v>16771.92</v>
       </c>
       <c r="N44" s="7">
         <v>0</v>
       </c>
       <c r="O44" s="5">
-        <v>12336.99</v>
+        <v>11343.08</v>
       </c>
       <c r="P44" s="7">
-        <v>56.10</v>
+        <v>59.70</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>20</v>
@@ -3507,16 +3507,16 @@
         <v>127285</v>
       </c>
       <c r="M46" s="7">
-        <v>92153.01</v>
+        <v>99133.84</v>
       </c>
       <c r="N46" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="O46" s="5">
-        <v>32131.99</v>
+        <v>28151.16</v>
       </c>
       <c r="P46" s="7">
-        <v>74.80</v>
+        <v>77.90</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>20</v>
@@ -3560,16 +3560,16 @@
         <v>24890</v>
       </c>
       <c r="M47" s="7">
-        <v>24329.58</v>
+        <v>24569.26</v>
       </c>
       <c r="N47" s="7">
         <v>0</v>
       </c>
       <c r="O47" s="5">
-        <v>560.42</v>
+        <v>320.74</v>
       </c>
       <c r="P47" s="7">
-        <v>97.70</v>
+        <v>98.70</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>20</v>
@@ -3613,13 +3613,13 @@
         <v>215021</v>
       </c>
       <c r="M48" s="7">
-        <v>131203.27</v>
+        <v>149847.98</v>
       </c>
       <c r="N48" s="7">
-        <v>21072.83</v>
+        <v>2483.34</v>
       </c>
       <c r="O48" s="5">
-        <v>62744.90</v>
+        <v>62689.68</v>
       </c>
       <c r="P48" s="7">
         <v>70.80</v>
@@ -3872,22 +3872,22 @@
         <v>0</v>
       </c>
       <c r="K53" s="5">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="L53" s="5">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="M53" s="7">
         <v>9725</v>
       </c>
       <c r="N53" s="7">
-        <v>0</v>
+        <v>25800</v>
       </c>
       <c r="O53" s="5">
         <v>-9725</v>
       </c>
       <c r="P53" s="7">
-        <v>100</v>
+        <v>137.70</v>
       </c>
       <c r="Q53" s="3" t="s">
         <v>27</v>
@@ -3984,16 +3984,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M55" s="7">
-        <v>13511242.609999999</v>
+        <v>14099882.140000001</v>
       </c>
       <c r="N55" s="7">
-        <v>414372.03</v>
+        <v>349329.07</v>
       </c>
       <c r="O55" s="5">
-        <v>1747484.13</v>
+        <v>1223887.56</v>
       </c>
       <c r="P55" s="7">
-        <v>88.90</v>
+        <v>92.20</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>27</v>
@@ -4037,16 +4037,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M56" s="7">
-        <v>13511242.609999999</v>
+        <v>14099882.140000001</v>
       </c>
       <c r="N56" s="7">
-        <v>414372.03</v>
+        <v>349329.07</v>
       </c>
       <c r="O56" s="5">
-        <v>1747484.13</v>
+        <v>1223887.56</v>
       </c>
       <c r="P56" s="7">
-        <v>88.90</v>
+        <v>92.20</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>27</v>
@@ -4143,16 +4143,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M58" s="7">
-        <v>13511242.609999999</v>
+        <v>14099882.140000001</v>
       </c>
       <c r="N58" s="7">
-        <v>414372.03</v>
+        <v>349329.07</v>
       </c>
       <c r="O58" s="5">
-        <v>1747484.13</v>
+        <v>1223887.56</v>
       </c>
       <c r="P58" s="7">
-        <v>88.90</v>
+        <v>92.20</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>27</v>
@@ -4196,16 +4196,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M59" s="7">
-        <v>13511242.609999999</v>
+        <v>14099882.140000001</v>
       </c>
       <c r="N59" s="7">
-        <v>414372.03</v>
+        <v>349329.07</v>
       </c>
       <c r="O59" s="5">
-        <v>1747484.13</v>
+        <v>1223887.56</v>
       </c>
       <c r="P59" s="7">
-        <v>88.90</v>
+        <v>92.20</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>27</v>

--- a/data/ytd-budget.xlsx
+++ b/data/ytd-budget.xlsx
@@ -1061,7 +1061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56107a29-9e84-47c9-938d-f3dcadf42edb}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594be50d-dceb-44ca-b416-5afddebf1c39}">
   <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -1175,16 +1175,16 @@
         <v>8292176</v>
       </c>
       <c r="M2" s="7">
-        <v>7516766.8600000003</v>
+        <v>7822022.5999999996</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>775409.14</v>
+        <v>470153.40</v>
       </c>
       <c r="P2" s="7">
-        <v>90.60</v>
+        <v>94.30</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>20</v>
@@ -1228,16 +1228,16 @@
         <v>839233</v>
       </c>
       <c r="M3" s="7">
-        <v>1026985</v>
+        <v>1087565.35</v>
       </c>
       <c r="N3" s="7">
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <v>-187752</v>
+        <v>-248332.35</v>
       </c>
       <c r="P3" s="7">
-        <v>122.40</v>
+        <v>129.60</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>27</v>
@@ -1440,19 +1440,19 @@
         <v>5304</v>
       </c>
       <c r="M7" s="7">
-        <v>5304</v>
+        <v>5746</v>
       </c>
       <c r="N7" s="7">
         <v>0</v>
       </c>
       <c r="O7" s="5">
-        <v>0</v>
+        <v>-442</v>
       </c>
       <c r="P7" s="7">
-        <v>100</v>
+        <v>108.30</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="12.75">
@@ -1546,16 +1546,16 @@
         <v>16200</v>
       </c>
       <c r="M9" s="7">
-        <v>17250</v>
+        <v>17925</v>
       </c>
       <c r="N9" s="7">
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <v>-1050</v>
+        <v>-1725</v>
       </c>
       <c r="P9" s="7">
-        <v>106.50</v>
+        <v>110.60</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>27</v>
@@ -1599,16 +1599,16 @@
         <v>1461990</v>
       </c>
       <c r="M10" s="7">
-        <v>1363190.44</v>
+        <v>1420456.62</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
       </c>
       <c r="O10" s="5">
-        <v>98799.56</v>
+        <v>41533.38</v>
       </c>
       <c r="P10" s="7">
-        <v>93.20</v>
+        <v>97.20</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>20</v>
@@ -1652,19 +1652,19 @@
         <v>652766</v>
       </c>
       <c r="M11" s="7">
-        <v>634182.67</v>
+        <v>660871.96</v>
       </c>
       <c r="N11" s="7">
         <v>0</v>
       </c>
       <c r="O11" s="5">
-        <v>18583.33</v>
+        <v>-8105.96</v>
       </c>
       <c r="P11" s="7">
-        <v>97.20</v>
+        <v>101.20</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="12.75">
@@ -1758,16 +1758,16 @@
         <v>1169536</v>
       </c>
       <c r="M13" s="7">
-        <v>966140.27</v>
+        <v>1010126.12</v>
       </c>
       <c r="N13" s="7">
         <v>0</v>
       </c>
       <c r="O13" s="5">
-        <v>203395.73</v>
+        <v>159409.88</v>
       </c>
       <c r="P13" s="7">
-        <v>82.60</v>
+        <v>86.40</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>20</v>
@@ -1811,16 +1811,16 @@
         <v>68758</v>
       </c>
       <c r="M14" s="7">
-        <v>39284.18</v>
+        <v>41798.29</v>
       </c>
       <c r="N14" s="7">
         <v>0</v>
       </c>
       <c r="O14" s="5">
-        <v>29473.82</v>
+        <v>26959.71</v>
       </c>
       <c r="P14" s="7">
-        <v>57.10</v>
+        <v>60.80</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>20</v>
@@ -1864,19 +1864,19 @@
         <v>157601</v>
       </c>
       <c r="M15" s="7">
-        <v>154500.79</v>
+        <v>160765.21</v>
       </c>
       <c r="N15" s="7">
         <v>0</v>
       </c>
       <c r="O15" s="5">
-        <v>3100.21</v>
+        <v>-3164.21</v>
       </c>
       <c r="P15" s="7">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="12.75">
@@ -1917,16 +1917,16 @@
         <v>42756</v>
       </c>
       <c r="M16" s="7">
-        <v>66145.86</v>
+        <v>65812.49</v>
       </c>
       <c r="N16" s="7">
         <v>0</v>
       </c>
       <c r="O16" s="5">
-        <v>-23389.86</v>
+        <v>-23056.49</v>
       </c>
       <c r="P16" s="7">
-        <v>154.70</v>
+        <v>153.90</v>
       </c>
       <c r="Q16" s="3" t="s">
         <v>27</v>
@@ -2288,13 +2288,13 @@
         <v>186358</v>
       </c>
       <c r="M23" s="7">
-        <v>146689.26</v>
+        <v>147493.73</v>
       </c>
       <c r="N23" s="7">
-        <v>26519.68</v>
+        <v>25570.88</v>
       </c>
       <c r="O23" s="5">
-        <v>13149.06</v>
+        <v>13293.39</v>
       </c>
       <c r="P23" s="7">
         <v>92.90</v>
@@ -2394,16 +2394,16 @@
         <v>100606</v>
       </c>
       <c r="M25" s="7">
-        <v>64304.68</v>
+        <v>75052.87</v>
       </c>
       <c r="N25" s="7">
-        <v>11789.19</v>
+        <v>3721</v>
       </c>
       <c r="O25" s="5">
-        <v>24512.13</v>
+        <v>21832.13</v>
       </c>
       <c r="P25" s="7">
-        <v>75.60</v>
+        <v>78.30</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>20</v>
@@ -2450,13 +2450,13 @@
         <v>101187.97</v>
       </c>
       <c r="N26" s="7">
-        <v>13344.46</v>
+        <v>13939.06</v>
       </c>
       <c r="O26" s="5">
-        <v>31767.57</v>
+        <v>31172.97</v>
       </c>
       <c r="P26" s="7">
-        <v>78.30</v>
+        <v>78.70</v>
       </c>
       <c r="Q26" s="3" t="s">
         <v>20</v>
@@ -2500,16 +2500,16 @@
         <v>181466</v>
       </c>
       <c r="M27" s="7">
-        <v>66880.95</v>
+        <v>104490.20</v>
       </c>
       <c r="N27" s="7">
-        <v>71753.50</v>
+        <v>36673.50</v>
       </c>
       <c r="O27" s="5">
-        <v>42831.55</v>
+        <v>40302.30</v>
       </c>
       <c r="P27" s="7">
-        <v>76.40</v>
+        <v>77.80</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>20</v>
@@ -2553,16 +2553,16 @@
         <v>235220</v>
       </c>
       <c r="M28" s="7">
-        <v>163614.79</v>
+        <v>197338.92</v>
       </c>
       <c r="N28" s="7">
-        <v>123987.33</v>
+        <v>93132.64</v>
       </c>
       <c r="O28" s="5">
-        <v>-52382.12</v>
+        <v>-55251.56</v>
       </c>
       <c r="P28" s="7">
-        <v>122.30</v>
+        <v>123.50</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>27</v>
@@ -2712,19 +2712,19 @@
         <v>98461.77</v>
       </c>
       <c r="M31" s="7">
-        <v>88384.44</v>
+        <v>100562.02</v>
       </c>
       <c r="N31" s="7">
         <v>0</v>
       </c>
       <c r="O31" s="5">
-        <v>10077.33</v>
+        <v>-2100.25</v>
       </c>
       <c r="P31" s="7">
-        <v>89.80</v>
+        <v>102.10</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="12.75">
@@ -2768,13 +2768,13 @@
         <v>529318.50</v>
       </c>
       <c r="N32" s="7">
-        <v>38570</v>
+        <v>0</v>
       </c>
       <c r="O32" s="5">
-        <v>-53176.50</v>
+        <v>-14606.50</v>
       </c>
       <c r="P32" s="7">
-        <v>110.30</v>
+        <v>102.80</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>27</v>
@@ -3136,16 +3136,16 @@
         <v>280967</v>
       </c>
       <c r="M39" s="7">
-        <v>171749.98</v>
+        <v>179484.65</v>
       </c>
       <c r="N39" s="7">
-        <v>16827.75</v>
+        <v>4318.08</v>
       </c>
       <c r="O39" s="5">
-        <v>92389.27</v>
+        <v>97164.27</v>
       </c>
       <c r="P39" s="7">
-        <v>67.10</v>
+        <v>65.40</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>20</v>
@@ -3242,16 +3242,16 @@
         <v>21468</v>
       </c>
       <c r="M41" s="7">
-        <v>28615.60</v>
+        <v>29085.87</v>
       </c>
       <c r="N41" s="7">
         <v>0</v>
       </c>
       <c r="O41" s="5">
-        <v>-7147.60</v>
+        <v>-7617.87</v>
       </c>
       <c r="P41" s="7">
-        <v>133.30</v>
+        <v>135.50</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>27</v>
@@ -3507,13 +3507,13 @@
         <v>127285</v>
       </c>
       <c r="M46" s="7">
-        <v>99133.84</v>
+        <v>99190.33</v>
       </c>
       <c r="N46" s="7">
         <v>0</v>
       </c>
       <c r="O46" s="5">
-        <v>28151.16</v>
+        <v>28094.67</v>
       </c>
       <c r="P46" s="7">
         <v>77.90</v>
@@ -3613,16 +3613,16 @@
         <v>215021</v>
       </c>
       <c r="M48" s="7">
-        <v>149847.98</v>
+        <v>153419.33</v>
       </c>
       <c r="N48" s="7">
-        <v>2483.34</v>
+        <v>2118.74</v>
       </c>
       <c r="O48" s="5">
-        <v>62689.68</v>
+        <v>59482.93</v>
       </c>
       <c r="P48" s="7">
-        <v>70.80</v>
+        <v>72.30</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>20</v>
@@ -3878,10 +3878,10 @@
         <v>25800</v>
       </c>
       <c r="M53" s="7">
-        <v>9725</v>
+        <v>35525</v>
       </c>
       <c r="N53" s="7">
-        <v>25800</v>
+        <v>0</v>
       </c>
       <c r="O53" s="5">
         <v>-9725</v>
@@ -3984,16 +3984,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M55" s="7">
-        <v>14099882.140000001</v>
+        <v>14735918.109999999</v>
       </c>
       <c r="N55" s="7">
-        <v>349329.07</v>
+        <v>197727.72</v>
       </c>
       <c r="O55" s="5">
-        <v>1223887.56</v>
+        <v>739452.94</v>
       </c>
       <c r="P55" s="7">
-        <v>92.20</v>
+        <v>95.30</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>27</v>
@@ -4037,16 +4037,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M56" s="7">
-        <v>14099882.140000001</v>
+        <v>14735918.109999999</v>
       </c>
       <c r="N56" s="7">
-        <v>349329.07</v>
+        <v>197727.72</v>
       </c>
       <c r="O56" s="5">
-        <v>1223887.56</v>
+        <v>739452.94</v>
       </c>
       <c r="P56" s="7">
-        <v>92.20</v>
+        <v>95.30</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>27</v>
@@ -4143,16 +4143,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M58" s="7">
-        <v>14099882.140000001</v>
+        <v>14735918.109999999</v>
       </c>
       <c r="N58" s="7">
-        <v>349329.07</v>
+        <v>197727.72</v>
       </c>
       <c r="O58" s="5">
-        <v>1223887.56</v>
+        <v>739452.94</v>
       </c>
       <c r="P58" s="7">
-        <v>92.20</v>
+        <v>95.30</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>27</v>
@@ -4196,16 +4196,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M59" s="7">
-        <v>14099882.140000001</v>
+        <v>14735918.109999999</v>
       </c>
       <c r="N59" s="7">
-        <v>349329.07</v>
+        <v>197727.72</v>
       </c>
       <c r="O59" s="5">
-        <v>1223887.56</v>
+        <v>739452.94</v>
       </c>
       <c r="P59" s="7">
-        <v>92.20</v>
+        <v>95.30</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>27</v>

--- a/data/ytd-budget.xlsx
+++ b/data/ytd-budget.xlsx
@@ -233,7 +233,7 @@
     <t>100-30-340-5041-</t>
   </si>
   <si>
-    <t>ARPA Salaries/Wages Transfer</t>
+    <t>Salaries/Wages Transfer</t>
   </si>
   <si>
     <t>5042</t>
@@ -242,7 +242,7 @@
     <t>100-30-340-5042-</t>
   </si>
   <si>
-    <t>ARPA Benefits Transfer</t>
+    <t>Benefits Transfer</t>
   </si>
   <si>
     <t>5101</t>
@@ -1061,7 +1061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{594be50d-dceb-44ca-b416-5afddebf1c39}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95df1714-7c56-4f60-b64d-39d8d451cfb2}">
   <dimension ref="A1:Q59"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
@@ -1175,16 +1175,16 @@
         <v>8292176</v>
       </c>
       <c r="M2" s="7">
-        <v>7822022.5999999996</v>
+        <v>8132049.8300000001</v>
       </c>
       <c r="N2" s="7">
         <v>0</v>
       </c>
       <c r="O2" s="5">
-        <v>470153.40</v>
+        <v>160126.17</v>
       </c>
       <c r="P2" s="7">
-        <v>94.30</v>
+        <v>98.10</v>
       </c>
       <c r="Q2" s="3" t="s">
         <v>20</v>
@@ -1228,16 +1228,16 @@
         <v>839233</v>
       </c>
       <c r="M3" s="7">
-        <v>1087565.35</v>
+        <v>1138026.13</v>
       </c>
       <c r="N3" s="7">
         <v>0</v>
       </c>
       <c r="O3" s="5">
-        <v>-248332.35</v>
+        <v>-298793.13</v>
       </c>
       <c r="P3" s="7">
-        <v>129.60</v>
+        <v>135.60</v>
       </c>
       <c r="Q3" s="3" t="s">
         <v>27</v>
@@ -1493,16 +1493,16 @@
         <v>20000</v>
       </c>
       <c r="M8" s="7">
-        <v>5784.51</v>
+        <v>6162.66</v>
       </c>
       <c r="N8" s="7">
         <v>0</v>
       </c>
       <c r="O8" s="5">
-        <v>14215.49</v>
+        <v>13837.34</v>
       </c>
       <c r="P8" s="7">
-        <v>28.90</v>
+        <v>30.80</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>20</v>
@@ -1546,16 +1546,16 @@
         <v>16200</v>
       </c>
       <c r="M9" s="7">
-        <v>17925</v>
+        <v>18600</v>
       </c>
       <c r="N9" s="7">
         <v>0</v>
       </c>
       <c r="O9" s="5">
-        <v>-1725</v>
+        <v>-2400</v>
       </c>
       <c r="P9" s="7">
-        <v>110.60</v>
+        <v>114.80</v>
       </c>
       <c r="Q9" s="3" t="s">
         <v>27</v>
@@ -1599,19 +1599,19 @@
         <v>1461990</v>
       </c>
       <c r="M10" s="7">
-        <v>1420456.62</v>
+        <v>1476813.22</v>
       </c>
       <c r="N10" s="7">
         <v>0</v>
       </c>
       <c r="O10" s="5">
-        <v>41533.38</v>
+        <v>-14823.22</v>
       </c>
       <c r="P10" s="7">
-        <v>97.20</v>
+        <v>101</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="12.75">
@@ -1652,16 +1652,16 @@
         <v>652766</v>
       </c>
       <c r="M11" s="7">
-        <v>660871.96</v>
+        <v>687118.29</v>
       </c>
       <c r="N11" s="7">
         <v>0</v>
       </c>
       <c r="O11" s="5">
-        <v>-8105.96</v>
+        <v>-34352.29</v>
       </c>
       <c r="P11" s="7">
-        <v>101.20</v>
+        <v>105.30</v>
       </c>
       <c r="Q11" s="3" t="s">
         <v>27</v>
@@ -1705,16 +1705,16 @@
         <v>6178</v>
       </c>
       <c r="M12" s="7">
-        <v>13268.42</v>
+        <v>13314.27</v>
       </c>
       <c r="N12" s="7">
         <v>0</v>
       </c>
       <c r="O12" s="5">
-        <v>-7090.42</v>
+        <v>-7136.27</v>
       </c>
       <c r="P12" s="7">
-        <v>214.80</v>
+        <v>215.50</v>
       </c>
       <c r="Q12" s="3" t="s">
         <v>27</v>
@@ -1758,16 +1758,16 @@
         <v>1169536</v>
       </c>
       <c r="M13" s="7">
-        <v>1010126.12</v>
+        <v>1054111.97</v>
       </c>
       <c r="N13" s="7">
         <v>0</v>
       </c>
       <c r="O13" s="5">
-        <v>159409.88</v>
+        <v>115424.03</v>
       </c>
       <c r="P13" s="7">
-        <v>86.40</v>
+        <v>90.10</v>
       </c>
       <c r="Q13" s="3" t="s">
         <v>20</v>
@@ -1811,16 +1811,16 @@
         <v>68758</v>
       </c>
       <c r="M14" s="7">
-        <v>41798.29</v>
+        <v>44312.40</v>
       </c>
       <c r="N14" s="7">
         <v>0</v>
       </c>
       <c r="O14" s="5">
-        <v>26959.71</v>
+        <v>24445.60</v>
       </c>
       <c r="P14" s="7">
-        <v>60.80</v>
+        <v>64.40</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>20</v>
@@ -1864,16 +1864,16 @@
         <v>157601</v>
       </c>
       <c r="M15" s="7">
-        <v>160765.21</v>
+        <v>166915.92</v>
       </c>
       <c r="N15" s="7">
         <v>0</v>
       </c>
       <c r="O15" s="5">
-        <v>-3164.21</v>
+        <v>-9314.92</v>
       </c>
       <c r="P15" s="7">
-        <v>102</v>
+        <v>105.90</v>
       </c>
       <c r="Q15" s="3" t="s">
         <v>27</v>
@@ -2129,16 +2129,16 @@
         <v>5000</v>
       </c>
       <c r="M20" s="7">
-        <v>2725.29</v>
+        <v>2783.49</v>
       </c>
       <c r="N20" s="7">
         <v>0</v>
       </c>
       <c r="O20" s="5">
-        <v>2274.71</v>
+        <v>2216.51</v>
       </c>
       <c r="P20" s="7">
-        <v>54.50</v>
+        <v>55.70</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>20</v>
@@ -2182,16 +2182,16 @@
         <v>5023</v>
       </c>
       <c r="M21" s="7">
-        <v>2226.25</v>
+        <v>2876.23</v>
       </c>
       <c r="N21" s="7">
         <v>0</v>
       </c>
       <c r="O21" s="5">
-        <v>2796.75</v>
+        <v>2146.77</v>
       </c>
       <c r="P21" s="7">
-        <v>44.30</v>
+        <v>57.30</v>
       </c>
       <c r="Q21" s="3" t="s">
         <v>20</v>
@@ -2235,16 +2235,16 @@
         <v>11560</v>
       </c>
       <c r="M22" s="7">
-        <v>8908.88</v>
+        <v>10152.05</v>
       </c>
       <c r="N22" s="7">
         <v>0</v>
       </c>
       <c r="O22" s="5">
-        <v>2651.12</v>
+        <v>1407.95</v>
       </c>
       <c r="P22" s="7">
-        <v>77.10</v>
+        <v>87.80</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>20</v>
@@ -2288,16 +2288,16 @@
         <v>186358</v>
       </c>
       <c r="M23" s="7">
-        <v>147493.73</v>
+        <v>167987.82</v>
       </c>
       <c r="N23" s="7">
-        <v>25570.88</v>
+        <v>8186.38</v>
       </c>
       <c r="O23" s="5">
-        <v>13293.39</v>
+        <v>10183.80</v>
       </c>
       <c r="P23" s="7">
-        <v>92.90</v>
+        <v>94.50</v>
       </c>
       <c r="Q23" s="3" t="s">
         <v>20</v>
@@ -2341,16 +2341,16 @@
         <v>500</v>
       </c>
       <c r="M24" s="7">
-        <v>859.23</v>
+        <v>871.88</v>
       </c>
       <c r="N24" s="7">
         <v>0</v>
       </c>
       <c r="O24" s="5">
-        <v>-359.23</v>
+        <v>-371.88</v>
       </c>
       <c r="P24" s="7">
-        <v>171.80</v>
+        <v>174.40</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>27</v>
@@ -2394,16 +2394,16 @@
         <v>100606</v>
       </c>
       <c r="M25" s="7">
-        <v>75052.87</v>
+        <v>73412.07</v>
       </c>
       <c r="N25" s="7">
-        <v>3721</v>
+        <v>0</v>
       </c>
       <c r="O25" s="5">
-        <v>21832.13</v>
+        <v>27193.93</v>
       </c>
       <c r="P25" s="7">
-        <v>78.30</v>
+        <v>73</v>
       </c>
       <c r="Q25" s="3" t="s">
         <v>20</v>
@@ -2447,13 +2447,13 @@
         <v>146300</v>
       </c>
       <c r="M26" s="7">
-        <v>101187.97</v>
+        <v>109416.96</v>
       </c>
       <c r="N26" s="7">
-        <v>13939.06</v>
+        <v>5720.22</v>
       </c>
       <c r="O26" s="5">
-        <v>31172.97</v>
+        <v>31162.82</v>
       </c>
       <c r="P26" s="7">
         <v>78.70</v>
@@ -2500,16 +2500,16 @@
         <v>181466</v>
       </c>
       <c r="M27" s="7">
-        <v>104490.20</v>
+        <v>151665.76</v>
       </c>
       <c r="N27" s="7">
-        <v>36673.50</v>
+        <v>4373.50</v>
       </c>
       <c r="O27" s="5">
-        <v>40302.30</v>
+        <v>25426.74</v>
       </c>
       <c r="P27" s="7">
-        <v>77.80</v>
+        <v>86</v>
       </c>
       <c r="Q27" s="3" t="s">
         <v>20</v>
@@ -2553,16 +2553,16 @@
         <v>235220</v>
       </c>
       <c r="M28" s="7">
-        <v>197338.92</v>
+        <v>251448.55</v>
       </c>
       <c r="N28" s="7">
-        <v>93132.64</v>
+        <v>41415.47</v>
       </c>
       <c r="O28" s="5">
-        <v>-55251.56</v>
+        <v>-57644.02</v>
       </c>
       <c r="P28" s="7">
-        <v>123.50</v>
+        <v>124.50</v>
       </c>
       <c r="Q28" s="3" t="s">
         <v>27</v>
@@ -2606,16 +2606,16 @@
         <v>79716</v>
       </c>
       <c r="M29" s="7">
-        <v>71048.08</v>
+        <v>70438.24</v>
       </c>
       <c r="N29" s="7">
         <v>0</v>
       </c>
       <c r="O29" s="5">
-        <v>8667.92</v>
+        <v>9277.76</v>
       </c>
       <c r="P29" s="7">
-        <v>89.10</v>
+        <v>88.40</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>20</v>
@@ -2977,16 +2977,16 @@
         <v>3650</v>
       </c>
       <c r="M36" s="7">
-        <v>3210.58</v>
+        <v>3269.38</v>
       </c>
       <c r="N36" s="7">
         <v>0</v>
       </c>
       <c r="O36" s="5">
-        <v>439.42</v>
+        <v>380.62</v>
       </c>
       <c r="P36" s="7">
-        <v>88</v>
+        <v>89.60</v>
       </c>
       <c r="Q36" s="3" t="s">
         <v>20</v>
@@ -3083,16 +3083,16 @@
         <v>2550</v>
       </c>
       <c r="M38" s="7">
-        <v>1893.46</v>
+        <v>2436.76</v>
       </c>
       <c r="N38" s="7">
         <v>0</v>
       </c>
       <c r="O38" s="5">
-        <v>656.54</v>
+        <v>113.24</v>
       </c>
       <c r="P38" s="7">
-        <v>74.30</v>
+        <v>95.60</v>
       </c>
       <c r="Q38" s="3" t="s">
         <v>20</v>
@@ -3136,16 +3136,16 @@
         <v>280967</v>
       </c>
       <c r="M39" s="7">
-        <v>179484.65</v>
+        <v>196585.27</v>
       </c>
       <c r="N39" s="7">
-        <v>4318.08</v>
+        <v>0</v>
       </c>
       <c r="O39" s="5">
-        <v>97164.27</v>
+        <v>84381.73</v>
       </c>
       <c r="P39" s="7">
-        <v>65.40</v>
+        <v>70</v>
       </c>
       <c r="Q39" s="3" t="s">
         <v>20</v>
@@ -3295,10 +3295,10 @@
         <v>21300</v>
       </c>
       <c r="M42" s="7">
-        <v>14841.07</v>
+        <v>15412.68</v>
       </c>
       <c r="N42" s="7">
-        <v>6458.93</v>
+        <v>5887.32</v>
       </c>
       <c r="O42" s="5">
         <v>0</v>
@@ -3348,16 +3348,16 @@
         <v>14125</v>
       </c>
       <c r="M43" s="7">
-        <v>13003.26</v>
+        <v>13272.56</v>
       </c>
       <c r="N43" s="7">
         <v>0</v>
       </c>
       <c r="O43" s="5">
-        <v>1121.74</v>
+        <v>852.44</v>
       </c>
       <c r="P43" s="7">
-        <v>92.10</v>
+        <v>94</v>
       </c>
       <c r="Q43" s="3" t="s">
         <v>20</v>
@@ -3401,16 +3401,16 @@
         <v>28115</v>
       </c>
       <c r="M44" s="7">
-        <v>16771.92</v>
+        <v>17273.09</v>
       </c>
       <c r="N44" s="7">
         <v>0</v>
       </c>
       <c r="O44" s="5">
-        <v>11343.08</v>
+        <v>10841.91</v>
       </c>
       <c r="P44" s="7">
-        <v>59.70</v>
+        <v>61.40</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>20</v>
@@ -3507,16 +3507,16 @@
         <v>127285</v>
       </c>
       <c r="M46" s="7">
-        <v>99190.33</v>
+        <v>106168.02</v>
       </c>
       <c r="N46" s="7">
         <v>0</v>
       </c>
       <c r="O46" s="5">
-        <v>28094.67</v>
+        <v>21116.98</v>
       </c>
       <c r="P46" s="7">
-        <v>77.90</v>
+        <v>83.40</v>
       </c>
       <c r="Q46" s="3" t="s">
         <v>20</v>
@@ -3560,16 +3560,16 @@
         <v>24890</v>
       </c>
       <c r="M47" s="7">
-        <v>24569.26</v>
+        <v>24714.17</v>
       </c>
       <c r="N47" s="7">
         <v>0</v>
       </c>
       <c r="O47" s="5">
-        <v>320.74</v>
+        <v>175.83</v>
       </c>
       <c r="P47" s="7">
-        <v>98.70</v>
+        <v>99.30</v>
       </c>
       <c r="Q47" s="3" t="s">
         <v>20</v>
@@ -3613,16 +3613,16 @@
         <v>215021</v>
       </c>
       <c r="M48" s="7">
-        <v>153419.33</v>
+        <v>170260.13</v>
       </c>
       <c r="N48" s="7">
-        <v>2118.74</v>
+        <v>0</v>
       </c>
       <c r="O48" s="5">
-        <v>59482.93</v>
+        <v>44760.87</v>
       </c>
       <c r="P48" s="7">
-        <v>72.30</v>
+        <v>79.20</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>20</v>
@@ -3666,16 +3666,16 @@
         <v>1650</v>
       </c>
       <c r="M49" s="7">
-        <v>298.89</v>
+        <v>631.67</v>
       </c>
       <c r="N49" s="7">
         <v>0</v>
       </c>
       <c r="O49" s="5">
-        <v>1351.11</v>
+        <v>1018.33</v>
       </c>
       <c r="P49" s="7">
-        <v>18.10</v>
+        <v>38.30</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>20</v>
@@ -3984,16 +3984,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M55" s="7">
-        <v>14735918.109999999</v>
+        <v>15405821.33</v>
       </c>
       <c r="N55" s="7">
-        <v>197727.72</v>
+        <v>77377.78</v>
       </c>
       <c r="O55" s="5">
-        <v>739452.94</v>
+        <v>189899.66</v>
       </c>
       <c r="P55" s="7">
-        <v>95.30</v>
+        <v>98.80</v>
       </c>
       <c r="Q55" s="3" t="s">
         <v>27</v>
@@ -4037,16 +4037,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M56" s="7">
-        <v>14735918.109999999</v>
+        <v>15405821.33</v>
       </c>
       <c r="N56" s="7">
-        <v>197727.72</v>
+        <v>77377.78</v>
       </c>
       <c r="O56" s="5">
-        <v>739452.94</v>
+        <v>189899.66</v>
       </c>
       <c r="P56" s="7">
-        <v>95.30</v>
+        <v>98.80</v>
       </c>
       <c r="Q56" s="3" t="s">
         <v>27</v>
@@ -4143,16 +4143,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M58" s="7">
-        <v>14735918.109999999</v>
+        <v>15405821.33</v>
       </c>
       <c r="N58" s="7">
-        <v>197727.72</v>
+        <v>77377.78</v>
       </c>
       <c r="O58" s="5">
-        <v>739452.94</v>
+        <v>189899.66</v>
       </c>
       <c r="P58" s="7">
-        <v>95.30</v>
+        <v>98.80</v>
       </c>
       <c r="Q58" s="3" t="s">
         <v>27</v>
@@ -4196,16 +4196,16 @@
         <v>15673098.77</v>
       </c>
       <c r="M59" s="7">
-        <v>14735918.109999999</v>
+        <v>15405821.33</v>
       </c>
       <c r="N59" s="7">
-        <v>197727.72</v>
+        <v>77377.78</v>
       </c>
       <c r="O59" s="5">
-        <v>739452.94</v>
+        <v>189899.66</v>
       </c>
       <c r="P59" s="7">
-        <v>95.30</v>
+        <v>98.80</v>
       </c>
       <c r="Q59" s="3" t="s">
         <v>27</v>
